--- a/otimizacao/data/itens_cardapio.xlsx
+++ b/otimizacao/data/itens_cardapio.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,16 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>a_base_de_ovos</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>P_bruto</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>P_origem</t>
         </is>
       </c>
     </row>
@@ -495,6 +505,12 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,6 +539,12 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +573,12 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,7 +592,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.9006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -591,6 +619,14 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
+      <c r="K5" t="n">
+        <v>-161.2845695779357</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,7 +640,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -631,6 +667,14 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
+      <c r="K6" t="n">
+        <v>-455.5444202475169</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -644,7 +688,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>1.0827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -671,6 +715,14 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="K7" t="n">
+        <v>-27.57733616977115</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -684,7 +736,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>1.115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -711,6 +763,14 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
+      <c r="K8" t="n">
+        <v>-3.809388748377773</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -724,7 +784,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>1.2023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -751,6 +811,14 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
+      <c r="K9" t="n">
+        <v>60.28144686984216</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -764,7 +832,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0.9799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -791,6 +859,14 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
+      <c r="K10" t="n">
+        <v>-103.0833607388118</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -804,7 +880,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>1.3563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -831,6 +907,14 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
+      <c r="K11" t="n">
+        <v>173.443675570787</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -844,7 +928,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>1.0696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -871,6 +955,14 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
+      <c r="K12" t="n">
+        <v>-37.1959509277151</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -884,7 +976,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.1476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -911,6 +1003,14 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
+      <c r="K13" t="n">
+        <v>20.13419917788499</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -924,7 +1024,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>1.1031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -951,6 +1051,14 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
+      <c r="K14" t="n">
+        <v>-12.54530866880844</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -964,7 +1072,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -991,6 +1099,14 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
+      <c r="K15" t="n">
+        <v>278.9586063929384</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1031,6 +1147,12 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1044,7 +1166,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>1.1731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1071,6 +1193,14 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
+      <c r="K17" t="n">
+        <v>38.8561847988078</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1084,7 +1214,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.9799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1111,6 +1241,14 @@
       <c r="J18" t="n">
         <v>0</v>
       </c>
+      <c r="K18" t="n">
+        <v>-103.0833607388118</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1124,7 +1262,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>1.0696</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1151,6 +1289,14 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
+      <c r="K19" t="n">
+        <v>-37.1959509277151</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1164,7 +1310,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>1.211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1191,6 +1337,14 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
+      <c r="K20" t="n">
+        <v>66.71991288260227</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1204,7 +1358,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>1.324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1231,6 +1385,14 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
+      <c r="K21" t="n">
+        <v>149.7024641643002</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1271,6 +1433,12 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1311,6 +1479,12 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1324,7 +1498,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>1.0811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1351,6 +1525,14 @@
       <c r="J24" t="n">
         <v>0</v>
       </c>
+      <c r="K24" t="n">
+        <v>-28.71908902499739</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1364,7 +1546,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>1.2311</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1391,6 +1573,14 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
+      <c r="K25" t="n">
+        <v>81.48047785743567</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1404,7 +1594,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>1.4014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1431,6 +1621,14 @@
       <c r="J26" t="n">
         <v>0</v>
       </c>
+      <c r="K26" t="n">
+        <v>206.5482550117944</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1444,7 +1642,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>1.1472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1471,6 +1669,14 @@
       <c r="J27" t="n">
         <v>0</v>
       </c>
+      <c r="K27" t="n">
+        <v>19.82194859106264</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1484,7 +1690,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>1.039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1511,6 +1717,14 @@
       <c r="J28" t="n">
         <v>0</v>
       </c>
+      <c r="K28" t="n">
+        <v>-59.6635961493805</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1524,7 +1738,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.9586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1551,6 +1765,14 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
+      <c r="K29" t="n">
+        <v>-118.6997439155508</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1564,7 +1786,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>1.0605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1591,6 +1813,14 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
+      <c r="K30" t="n">
+        <v>-43.86140324719656</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1604,7 +1834,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>1.1718</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1631,6 +1861,14 @@
       <c r="J31" t="n">
         <v>0</v>
       </c>
+      <c r="K31" t="n">
+        <v>37.88012598006974</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1644,7 +1882,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>1.2814</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1671,6 +1909,14 @@
       <c r="J32" t="n">
         <v>0</v>
       </c>
+      <c r="K32" t="n">
+        <v>118.4269396001465</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1684,7 +1930,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0.8825</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1707,6 +1953,14 @@
       <c r="J33" t="n">
         <v>0</v>
       </c>
+      <c r="K33" t="n">
+        <v>-29.17303561829389</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1720,7 +1974,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0.7915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1743,6 +1997,14 @@
       <c r="J34" t="n">
         <v>0</v>
       </c>
+      <c r="K34" t="n">
+        <v>-64.92355117139336</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1756,7 +2018,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>1.0162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1779,6 +2041,14 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
+      <c r="K35" t="n">
+        <v>23.30119896524576</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1792,7 +2062,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0.9504</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1815,6 +2085,14 @@
       <c r="J36" t="n">
         <v>0</v>
       </c>
+      <c r="K36" t="n">
+        <v>-2.543758762705908</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1828,7 +2106,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>1.1242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1851,6 +2129,14 @@
       <c r="J37" t="n">
         <v>0</v>
       </c>
+      <c r="K37" t="n">
+        <v>65.6837495013025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1887,6 +2173,12 @@
       <c r="J38" t="n">
         <v>0</v>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1900,7 +2192,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0.8875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1923,6 +2215,14 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
+      <c r="K39" t="n">
+        <v>-27.24387610500032</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1936,7 +2236,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1959,6 +2259,14 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
+      <c r="K40" t="n">
+        <v>28.70148939344737</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1972,7 +2280,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>1.0544</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1995,6 +2303,14 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
+      <c r="K41" t="n">
+        <v>38.29695104533869</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2031,6 +2347,12 @@
       <c r="J42" t="n">
         <v>0</v>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2044,7 +2366,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0.8941</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2067,6 +2389,14 @@
       <c r="J43" t="n">
         <v>0</v>
       </c>
+      <c r="K43" t="n">
+        <v>-24.63896364886654</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2080,7 +2410,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>1.162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2103,6 +2433,14 @@
       <c r="J44" t="n">
         <v>0</v>
       </c>
+      <c r="K44" t="n">
+        <v>80.54788095598771</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2116,7 +2454,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>1.0638</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2139,6 +2477,14 @@
       <c r="J45" t="n">
         <v>0</v>
       </c>
+      <c r="K45" t="n">
+        <v>41.98280083955225</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2152,7 +2498,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0.8425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2175,6 +2521,14 @@
       <c r="J46" t="n">
         <v>0</v>
       </c>
+      <c r="K46" t="n">
+        <v>-44.87845442081395</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2188,7 +2542,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>1.0467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2211,6 +2565,14 @@
       <c r="J47" t="n">
         <v>0</v>
       </c>
+      <c r="K47" t="n">
+        <v>35.27483033635507</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2224,7 +2586,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0.9437</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2247,6 +2609,14 @@
       <c r="J48" t="n">
         <v>0</v>
       </c>
+      <c r="K48" t="n">
+        <v>-5.177451492096583</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2260,7 +2630,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>1.1855</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2283,6 +2653,14 @@
       <c r="J49" t="n">
         <v>0</v>
       </c>
+      <c r="K49" t="n">
+        <v>89.7772120719645</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2296,7 +2674,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0.9648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2319,6 +2697,14 @@
       <c r="J50" t="n">
         <v>0</v>
       </c>
+      <c r="K50" t="n">
+        <v>3.104228590196279</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2332,7 +2718,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0.8613</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2355,6 +2741,14 @@
       <c r="J51" t="n">
         <v>0</v>
       </c>
+      <c r="K51" t="n">
+        <v>-37.49342832959428</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2368,7 +2762,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0.9545</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2391,6 +2785,14 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
+      <c r="K52" t="n">
+        <v>-0.9203405828450386</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2404,7 +2806,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>1.1274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2427,6 +2829,14 @@
       <c r="J53" t="n">
         <v>0</v>
       </c>
+      <c r="K53" t="n">
+        <v>66.95139581305838</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2440,7 +2850,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0.7971</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2463,6 +2873,14 @@
       <c r="J54" t="n">
         <v>0</v>
       </c>
+      <c r="K54" t="n">
+        <v>-62.72550378489314</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2476,7 +2894,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0.865</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2499,6 +2917,14 @@
       <c r="J55" t="n">
         <v>0</v>
       </c>
+      <c r="K55" t="n">
+        <v>-36.07585297622565</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2512,7 +2938,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2535,6 +2961,14 @@
       <c r="J56" t="n">
         <v>0</v>
       </c>
+      <c r="K56" t="n">
+        <v>213.2334678409768</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2571,6 +3005,12 @@
       <c r="J57" t="n">
         <v>0</v>
       </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2584,7 +3024,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>1.236</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2607,6 +3047,14 @@
       <c r="J58" t="n">
         <v>0</v>
       </c>
+      <c r="K58" t="n">
+        <v>109.5846657250077</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2620,7 +3068,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>1.0233</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2643,6 +3091,14 @@
       <c r="J59" t="n">
         <v>0</v>
       </c>
+      <c r="K59" t="n">
+        <v>26.07544749300257</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2656,7 +3112,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0.9619</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2679,6 +3135,14 @@
       <c r="J60" t="n">
         <v>0</v>
       </c>
+      <c r="K60" t="n">
+        <v>1.963282104044734</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2715,6 +3179,12 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2728,7 +3198,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0.9103</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2751,6 +3221,14 @@
       <c r="J62" t="n">
         <v>0</v>
       </c>
+      <c r="K62" t="n">
+        <v>-18.28110262593783</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2764,7 +3242,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0.8068</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2787,6 +3265,14 @@
       <c r="J63" t="n">
         <v>0</v>
       </c>
+      <c r="K63" t="n">
+        <v>-58.89324508375891</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2800,7 +3286,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0.9467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2823,6 +3309,14 @@
       <c r="J64" t="n">
         <v>0</v>
       </c>
+      <c r="K64" t="n">
+        <v>-3.96998307638477</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2836,7 +3330,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0.8319</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2859,6 +3353,14 @@
       <c r="J65" t="n">
         <v>0</v>
       </c>
+      <c r="K65" t="n">
+        <v>-49.06996648872707</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2872,7 +3374,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2895,6 +3397,14 @@
       <c r="J66" t="n">
         <v>0</v>
       </c>
+      <c r="K66" t="n">
+        <v>-179.35494809751</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2908,7 +3418,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0.9112</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2931,6 +3441,14 @@
       <c r="J67" t="n">
         <v>0</v>
       </c>
+      <c r="K67" t="n">
+        <v>-17.90997691764032</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2944,7 +3462,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>1.0107</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2967,6 +3485,14 @@
       <c r="J68" t="n">
         <v>0</v>
       </c>
+      <c r="K68" t="n">
+        <v>21.13835484974408</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2980,7 +3506,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3003,6 +3529,14 @@
       <c r="J69" t="n">
         <v>0</v>
       </c>
+      <c r="K69" t="n">
+        <v>3.986225241651442</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3016,7 +3550,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0.7992</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -3035,6 +3569,14 @@
       <c r="J70" t="n">
         <v>0</v>
       </c>
+      <c r="K70" t="n">
+        <v>-1.575063289865063</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3048,7 +3590,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0.6605</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -3067,6 +3609,14 @@
       <c r="J71" t="n">
         <v>0</v>
       </c>
+      <c r="K71" t="n">
+        <v>-36.78609842064056</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3080,7 +3630,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>1.0592</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -3099,6 +3649,14 @@
       <c r="J72" t="n">
         <v>0</v>
       </c>
+      <c r="K72" t="n">
+        <v>64.38361061336494</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3112,7 +3670,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0.8273</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
@@ -3135,6 +3693,14 @@
       <c r="J73" t="n">
         <v>0</v>
       </c>
+      <c r="K73" t="n">
+        <v>5.561318675725307</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3148,7 +3714,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0.8697</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
@@ -3171,6 +3737,14 @@
       <c r="J74" t="n">
         <v>0</v>
       </c>
+      <c r="K74" t="n">
+        <v>16.30774260112397</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3184,7 +3758,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0.8697</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
@@ -3207,6 +3781,14 @@
       <c r="J75" t="n">
         <v>0</v>
       </c>
+      <c r="K75" t="n">
+        <v>16.30774260112397</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3220,7 +3802,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0.8697</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
@@ -3243,6 +3825,14 @@
       <c r="J76" t="n">
         <v>0</v>
       </c>
+      <c r="K76" t="n">
+        <v>16.30774260112397</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3256,7 +3846,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
@@ -3279,6 +3869,14 @@
       <c r="J77" t="n">
         <v>0</v>
       </c>
+      <c r="K77" t="n">
+        <v>176.2357702991251</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3292,7 +3890,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0.7669</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
@@ -3315,6 +3913,14 @@
       <c r="J78" t="n">
         <v>0</v>
       </c>
+      <c r="K78" t="n">
+        <v>-9.789069116892737</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3328,7 +3934,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>1.2789</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -3347,6 +3953,14 @@
       <c r="J79" t="n">
         <v>0</v>
       </c>
+      <c r="K79" t="n">
+        <v>120.1465051674567</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3360,7 +3974,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
@@ -3383,6 +3997,14 @@
       <c r="J80" t="n">
         <v>0</v>
       </c>
+      <c r="K80" t="n">
+        <v>-77.49807038775498</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3396,7 +4018,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0.7993</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
@@ -3419,6 +4041,14 @@
       <c r="J81" t="n">
         <v>0</v>
       </c>
+      <c r="K81" t="n">
+        <v>-1.559355605760141</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3432,7 +4062,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0.5495</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
@@ -3455,6 +4085,14 @@
       <c r="J82" t="n">
         <v>0</v>
       </c>
+      <c r="K82" t="n">
+        <v>-64.93113536417188</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3468,7 +4106,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0.5495</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
@@ -3491,6 +4129,14 @@
       <c r="J83" t="n">
         <v>0</v>
       </c>
+      <c r="K83" t="n">
+        <v>-64.93113536417188</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3504,7 +4150,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0.5495</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
@@ -3527,6 +4173,14 @@
       <c r="J84" t="n">
         <v>0</v>
       </c>
+      <c r="K84" t="n">
+        <v>-64.93113536417188</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3540,7 +4194,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
@@ -3563,6 +4217,14 @@
       <c r="J85" t="n">
         <v>0</v>
       </c>
+      <c r="K85" t="n">
+        <v>-14.05473410940782</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3576,7 +4238,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0.6229</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
@@ -3599,6 +4261,14 @@
       <c r="J86" t="n">
         <v>0</v>
       </c>
+      <c r="K86" t="n">
+        <v>-46.31911728836002</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3612,7 +4282,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
@@ -3635,6 +4305,14 @@
       <c r="J87" t="n">
         <v>0</v>
       </c>
+      <c r="K87" t="n">
+        <v>-13.18529837506729</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3648,7 +4326,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0.8608</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
@@ -3671,6 +4349,14 @@
       <c r="J88" t="n">
         <v>0</v>
       </c>
+      <c r="K88" t="n">
+        <v>14.06014731831051</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3684,7 +4370,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
@@ -3707,6 +4393,14 @@
       <c r="J89" t="n">
         <v>0</v>
       </c>
+      <c r="K89" t="n">
+        <v>7.059286670512295</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3720,7 +4414,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>0.7493</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
@@ -3743,6 +4437,14 @@
       <c r="J90" t="n">
         <v>0</v>
       </c>
+      <c r="K90" t="n">
+        <v>-14.23209227428889</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3756,7 +4458,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0.8777</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
@@ -3779,6 +4481,14 @@
       <c r="J91" t="n">
         <v>0</v>
       </c>
+      <c r="K91" t="n">
+        <v>18.34777105614783</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3792,7 +4502,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0.8777</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
@@ -3815,6 +4525,14 @@
       <c r="J92" t="n">
         <v>0</v>
       </c>
+      <c r="K92" t="n">
+        <v>18.34777105614783</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3828,7 +4546,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0.8323</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
@@ -3851,6 +4569,14 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
+      <c r="K93" t="n">
+        <v>6.823662434535074</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3864,7 +4590,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
@@ -3887,6 +4613,14 @@
       <c r="J94" t="n">
         <v>0</v>
       </c>
+      <c r="K94" t="n">
+        <v>-1.40006106380389</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3900,7 +4634,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>1.1574</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -3919,6 +4653,14 @@
       <c r="J95" t="n">
         <v>0</v>
       </c>
+      <c r="K95" t="n">
+        <v>89.29611052020886</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3932,7 +4674,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0.5325</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -3951,6 +4693,14 @@
       <c r="J96" t="n">
         <v>0</v>
       </c>
+      <c r="K96" t="n">
+        <v>-69.23913545412927</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3964,7 +4714,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>1.1371</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
@@ -3987,6 +4737,14 @@
       <c r="J97" t="n">
         <v>0</v>
       </c>
+      <c r="K97" t="n">
+        <v>84.14926073807601</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4000,7 +4758,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0.7897</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -4015,6 +4773,14 @@
       <c r="J98" t="n">
         <v>0</v>
       </c>
+      <c r="K98" t="n">
+        <v>-5.830989106471744</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4028,7 +4794,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0.8616</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -4043,6 +4809,14 @@
       <c r="J99" t="n">
         <v>0</v>
       </c>
+      <c r="K99" t="n">
+        <v>11.01427351758278</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4056,7 +4830,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0.8599</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -4071,6 +4845,14 @@
       <c r="J100" t="n">
         <v>0</v>
       </c>
+      <c r="K100" t="n">
+        <v>10.61789105388403</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4084,7 +4866,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0.6115</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -4099,6 +4881,14 @@
       <c r="J101" t="n">
         <v>0</v>
       </c>
+      <c r="K101" t="n">
+        <v>-47.60258932957951</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4112,7 +4902,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0.9828</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
@@ -4127,6 +4917,14 @@
       <c r="J102" t="n">
         <v>0</v>
       </c>
+      <c r="K102" t="n">
+        <v>39.45145937651784</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4140,7 +4938,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>0.9071</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -4155,6 +4953,14 @@
       <c r="J103" t="n">
         <v>0</v>
       </c>
+      <c r="K103" t="n">
+        <v>21.70072469105358</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4168,7 +4974,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>0.958</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
@@ -4183,6 +4989,14 @@
       <c r="J104" t="n">
         <v>0</v>
       </c>
+      <c r="K104" t="n">
+        <v>33.62857987817632</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4196,7 +5010,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>0.6052</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -4211,6 +5025,14 @@
       <c r="J105" t="n">
         <v>0</v>
       </c>
+      <c r="K105" t="n">
+        <v>-49.09736970049685</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4224,7 +5046,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>0.8656</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
@@ -4239,6 +5061,14 @@
       <c r="J106" t="n">
         <v>0</v>
       </c>
+      <c r="K106" t="n">
+        <v>11.95760046773904</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4252,7 +5082,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0.7319</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -4267,6 +5097,14 @@
       <c r="J107" t="n">
         <v>0</v>
       </c>
+      <c r="K107" t="n">
+        <v>-19.37541061788215</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4280,7 +5118,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>0.9234</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -4295,6 +5133,14 @@
       <c r="J108" t="n">
         <v>0</v>
       </c>
+      <c r="K108" t="n">
+        <v>25.51081136895565</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4308,7 +5154,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>0.8696</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -4323,6 +5169,14 @@
       <c r="J109" t="n">
         <v>0</v>
       </c>
+      <c r="K109" t="n">
+        <v>12.89095505578417</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4336,7 +5190,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -4351,6 +5205,14 @@
       <c r="J110" t="n">
         <v>0</v>
       </c>
+      <c r="K110" t="n">
+        <v>-20.46969572320094</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4364,7 +5226,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>1.2716</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
@@ -4379,6 +5241,14 @@
       <c r="J111" t="n">
         <v>0</v>
       </c>
+      <c r="K111" t="n">
+        <v>107.1411038335903</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4392,7 +5262,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>0.615</v>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
@@ -4407,6 +5277,14 @@
       <c r="J112" t="n">
         <v>0</v>
       </c>
+      <c r="K112" t="n">
+        <v>-46.78076909324454</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4420,7 +5298,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0.8914</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
@@ -4435,6 +5313,14 @@
       <c r="J113" t="n">
         <v>0</v>
       </c>
+      <c r="K113" t="n">
+        <v>18.00997038686726</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4448,7 +5334,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>0.7066</v>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
@@ -4463,6 +5349,14 @@
       <c r="J114" t="n">
         <v>0</v>
       </c>
+      <c r="K114" t="n">
+        <v>-25.30425789197388</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4476,7 +5370,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>1.1893</v>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
@@ -4491,6 +5385,14 @@
       <c r="J115" t="n">
         <v>0</v>
       </c>
+      <c r="K115" t="n">
+        <v>87.84295176620876</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4504,7 +5406,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -4519,6 +5421,14 @@
       <c r="J116" t="n">
         <v>0</v>
       </c>
+      <c r="K116" t="n">
+        <v>-73.75384877242222</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4532,7 +5442,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0.6705</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -4547,6 +5457,14 @@
       <c r="J117" t="n">
         <v>0</v>
       </c>
+      <c r="K117" t="n">
+        <v>-33.76905902114827</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4560,7 +5478,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0.9333</v>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
@@ -4575,6 +5493,14 @@
       <c r="J118" t="n">
         <v>0</v>
       </c>
+      <c r="K118" t="n">
+        <v>27.82376135698228</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4588,7 +5514,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -4603,6 +5529,14 @@
       <c r="J119" t="n">
         <v>0</v>
       </c>
+      <c r="K119" t="n">
+        <v>-29.44644466157467</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4616,7 +5550,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>1.0136</v>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
@@ -4631,6 +5565,14 @@
       <c r="J120" t="n">
         <v>0</v>
       </c>
+      <c r="K120" t="n">
+        <v>46.66324484983235</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4644,7 +5586,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0.6159</v>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
@@ -4659,6 +5601,14 @@
       <c r="J121" t="n">
         <v>0</v>
       </c>
+      <c r="K121" t="n">
+        <v>-46.59052711040685</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4672,7 +5622,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0.6692</v>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
@@ -4687,6 +5637,14 @@
       <c r="J122" t="n">
         <v>0</v>
       </c>
+      <c r="K122" t="n">
+        <v>-34.07612958429395</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4700,7 +5658,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0.8671</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
@@ -4715,6 +5673,14 @@
       <c r="J123" t="n">
         <v>0</v>
       </c>
+      <c r="K123" t="n">
+        <v>12.32495581897302</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4728,7 +5694,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0.7244</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
@@ -4743,6 +5709,14 @@
       <c r="J124" t="n">
         <v>0</v>
       </c>
+      <c r="K124" t="n">
+        <v>-21.14879961002561</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4756,7 +5730,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>1.1481</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
@@ -4771,6 +5745,14 @@
       <c r="J125" t="n">
         <v>0</v>
       </c>
+      <c r="K125" t="n">
+        <v>78.20413147534025</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4784,7 +5766,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>1.0335</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
@@ -4799,6 +5781,14 @@
       <c r="J126" t="n">
         <v>0</v>
       </c>
+      <c r="K126" t="n">
+        <v>51.31890175130258</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4812,7 +5802,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
@@ -4827,6 +5817,14 @@
       <c r="J127" t="n">
         <v>0</v>
       </c>
+      <c r="K127" t="n">
+        <v>160.6992438181574</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4840,7 +5838,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0.7371</v>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
@@ -4855,6 +5853,14 @@
       <c r="J128" t="n">
         <v>0</v>
       </c>
+      <c r="K128" t="n">
+        <v>-18.15415336432833</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4868,7 +5874,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -4883,6 +5889,14 @@
       <c r="J129" t="n">
         <v>0</v>
       </c>
+      <c r="K129" t="n">
+        <v>-60.8900170648464</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4896,7 +5910,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0.9428</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -4911,6 +5925,14 @@
       <c r="J130" t="n">
         <v>0</v>
       </c>
+      <c r="K130" t="n">
+        <v>30.07157476993266</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4924,7 +5946,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
@@ -4939,6 +5961,14 @@
       <c r="J131" t="n">
         <v>0</v>
       </c>
+      <c r="K131" t="n">
+        <v>-28.23627102543525</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4952,7 +5982,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0.9588</v>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
@@ -4967,6 +5997,14 @@
       <c r="J132" t="n">
         <v>0</v>
       </c>
+      <c r="K132" t="n">
+        <v>33.81935615262645</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4980,7 +6018,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>1.072</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -4995,6 +6033,14 @@
       <c r="J133" t="n">
         <v>0</v>
       </c>
+      <c r="K133" t="n">
+        <v>60.34891700170505</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>exato</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5023,6 +6069,12 @@
       <c r="J134" t="n">
         <v>0</v>
       </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5036,7 +6088,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0.9234</v>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
@@ -5051,6 +6103,14 @@
       <c r="J135" t="n">
         <v>0</v>
       </c>
+      <c r="K135" t="n">
+        <v>25.51081136895565</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>herdado</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5079,6 +6139,12 @@
       <c r="J136" t="n">
         <v>0</v>
       </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5107,6 +6173,12 @@
       <c r="J137" t="n">
         <v>0</v>
       </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5135,6 +6207,12 @@
       <c r="J138" t="n">
         <v>0</v>
       </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5163,6 +6241,12 @@
       <c r="J139" t="n">
         <v>0</v>
       </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5191,6 +6275,12 @@
       <c r="J140" t="n">
         <v>0</v>
       </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5219,6 +6309,12 @@
       <c r="J141" t="n">
         <v>0</v>
       </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5247,6 +6343,12 @@
       <c r="J142" t="n">
         <v>0</v>
       </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5275,6 +6377,12 @@
       <c r="J143" t="n">
         <v>0</v>
       </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5303,6 +6411,12 @@
       <c r="J144" t="n">
         <v>0</v>
       </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5331,6 +6445,12 @@
       <c r="J145" t="n">
         <v>0</v>
       </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5359,6 +6479,12 @@
       <c r="J146" t="n">
         <v>0</v>
       </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>sem_dados</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5387,6 +6513,12 @@
       <c r="J147" t="n">
         <v>0</v>
       </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5415,6 +6547,12 @@
       <c r="J148" t="n">
         <v>0</v>
       </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5443,6 +6581,12 @@
       <c r="J149" t="n">
         <v>0</v>
       </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5471,6 +6615,12 @@
       <c r="J150" t="n">
         <v>0</v>
       </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5499,6 +6649,12 @@
       <c r="J151" t="n">
         <v>0</v>
       </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5527,6 +6683,12 @@
       <c r="J152" t="n">
         <v>0</v>
       </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5555,6 +6717,12 @@
       <c r="J153" t="n">
         <v>0</v>
       </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5583,6 +6751,12 @@
       <c r="J154" t="n">
         <v>0</v>
       </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5611,6 +6785,12 @@
       <c r="J155" t="n">
         <v>0</v>
       </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5639,6 +6819,12 @@
       <c r="J156" t="n">
         <v>0</v>
       </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>fora_do_dml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
